--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheckthresh.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheckthresh.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -35,20 +35,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,16 +140,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,16 +152,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,17 +769,17 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="n">
-        <v>11.1</v>
+      <c r="D4" s="8" t="n">
+        <v>0.1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="10" t="n">
         <v>23</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
@@ -808,25 +790,25 @@
       <c r="J4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M4" s="13" t="n">
-        <v>86.8</v>
+      <c r="L4" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>16.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q4" s="13" t="n">
+      <c r="Q4" s="8" t="n">
         <v>84</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -839,8 +821,8 @@
         <v>20.5</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr"/>
-      <c r="W4" s="11" t="inlineStr"/>
+      <c r="V4" s="10" t="inlineStr"/>
+      <c r="W4" s="10" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -858,18 +840,18 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D5" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -881,20 +863,20 @@
       <c r="J5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="M5" s="3" t="n">
+      <c r="L5" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M5" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>3.4</v>
@@ -914,10 +896,10 @@
       <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="V5" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -943,18 +925,18 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D6" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -966,20 +948,20 @@
       <c r="J6" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>3</v>
@@ -994,15 +976,15 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>58</v>
+        <v>56.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V6" s="11" t="n">
+      <c r="V6" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="10" t="n">
         <v>20</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1028,49 +1010,49 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D7" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>30.4</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="10" t="n">
         <v>24.1</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="10" t="n">
         <v>12.6</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="13" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="M7" s="14" t="n">
+      <c r="L7" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M7" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="13" t="n">
-        <v>0.4</v>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
@@ -1079,22 +1061,22 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>656.4</v>
+        <v>56.4</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="W7" s="11" t="n">
+      <c r="W7" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="14" t="n">
+      <c r="X7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>27.8</v>
+        <v>57.8</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>14</v>
@@ -1113,41 +1095,41 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>13.6</v>
+      <c r="D8" s="10" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>13.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>17.4</v>
+      <c r="L8" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>16.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>4</v>
@@ -1167,17 +1149,17 @@
       <c r="U8" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V8" s="11" t="n">
+      <c r="V8" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>19.4</v>
@@ -1197,7 +1179,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="9" t="n">
-        <v>148.8</v>
+        <v>145.8</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>887.1</v>
@@ -1206,24 +1188,24 @@
         <v>17.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="K9" s="11" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="10" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1236,16 +1218,16 @@
         <v>16</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>142.8</v>
+        <v>145.8</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>1196</v>
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>182.6</v>
+        <v>122.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9255.1</v>
+        <v>255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
@@ -1254,13 +1236,13 @@
         <v>127.2</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>971.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>26.2</v>
+        <v>56.2</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>67</v>
@@ -1279,16 +1261,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="10" t="n">
         <v>29.1</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="10" t="n">
         <v>11.5</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1298,15 +1280,15 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M10" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M10" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1325,25 +1307,25 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>90.5</v>
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="10" t="n">
         <v>19.5</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>5.9</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.4</v>
@@ -1362,13 +1344,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1378,19 +1360,19 @@
         <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="14" t="n">
-        <v>18.2</v>
+      <c r="M11" s="10" t="n">
+        <v>17.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
@@ -1401,10 +1383,10 @@
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" s="10" t="n">
         <v>20</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1414,19 +1396,19 @@
         <v>425.4</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="13" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>45.4</v>
       </c>
-      <c r="W11" s="13" t="n">
+      <c r="W11" s="8" t="n">
         <v>19.51</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>48.9</v>
+        <v>58.9</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1443,18 +1425,18 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D12" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="10" t="n">
         <v>10.2</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1466,40 +1448,40 @@
       <c r="J12" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q12" s="13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R12" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R12" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>257.1</v>
+        <v>57.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V12" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V12" s="8" t="n">
         <v>45.4</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1528,16 +1510,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1549,13 +1531,13 @@
       <c r="J13" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="11" t="n">
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1565,12 +1547,12 @@
         <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q13" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="R13" s="11" t="n">
+      <c r="R13" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1611,16 +1593,16 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1629,34 +1611,34 @@
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="14" t="n">
+      <c r="N14" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>714.5</v>
+        <v>74.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="14" t="n">
+      <c r="S14" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
@@ -1694,16 +1676,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G15" s="11" t="n">
+      <c r="E15" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1715,13 +1697,13 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1733,10 +1715,10 @@
       <c r="P15" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1779,20 +1761,20 @@
       <c r="C16" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="10" t="n">
         <v>138.8</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="10" t="n">
         <v>113.9</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="10" t="n">
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>288.2</v>
+        <v>84.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1800,32 +1782,32 @@
       <c r="J16" s="3" t="n">
         <v>50.6</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="9" t="n">
-        <v>92</v>
-      </c>
-      <c r="M16" s="9" t="n">
+      <c r="L16" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="M16" s="10" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>909.4</v>
+        <v>904.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>40</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="Q16" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Q16" s="10" t="n">
         <v>138.2</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" s="10" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98.8</v>
+        <v>988.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>66.8</v>
@@ -1843,10 +1825,10 @@
         <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>102</v>
+        <v>302</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1862,16 +1844,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="10" t="n">
         <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1884,50 +1866,50 @@
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="14" t="n">
-        <v>19.1</v>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q17" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R17" s="9" t="n">
-        <v>11.4</v>
+      <c r="Q17" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>1.7</v>
+        <v>17.2</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>15.5</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1068.5</v>
+        <v>120.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>810.8</v>
+        <v>902.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1943,15 +1925,15 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="10" t="n">
         <v>30.4</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="8" t="n">
         <v>44.5</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="8" t="n">
         <v>38.4</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1966,13 +1948,13 @@
       <c r="J18" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="13" t="n">
+      <c r="L18" s="8" t="n">
         <v>49.6</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="10" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1984,10 +1966,10 @@
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="13" t="n">
+      <c r="Q18" s="8" t="n">
         <v>90.47</v>
       </c>
-      <c r="R18" s="13" t="n">
+      <c r="R18" s="8" t="n">
         <v>44.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1999,20 +1981,20 @@
       <c r="U18" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V18" s="13" t="n">
+      <c r="V18" s="8" t="n">
         <v>46.47</v>
       </c>
-      <c r="W18" s="13" t="n">
+      <c r="W18" s="8" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>86</v>
+        <v>16.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2028,16 +2010,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="11" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E19" s="11" t="n">
+      <c r="D19" s="10" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="10" t="n">
         <v>23.7</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="10" t="n">
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2049,26 +2031,26 @@
       <c r="J19" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="14" t="n">
-        <v>18.1</v>
+      <c r="N19" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="13" t="n">
-        <v>92.59999999999999</v>
+      <c r="Q19" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2083,7 +2065,7 @@
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2092,7 +2074,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>294</v>
+        <v>28.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2111,22 +2093,22 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="10" t="n">
         <v>12.4</v>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>87.40000000000001</v>
+      <c r="H20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>7.9</v>
@@ -2134,20 +2116,20 @@
       <c r="J20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>0.8</v>
+      <c r="K20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>19</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.8</v>
@@ -2180,7 +2162,7 @@
         <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2196,16 +2178,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="10" t="n">
         <v>8.6</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2217,20 +2199,20 @@
       <c r="J21" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.8</v>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>2.8</v>
@@ -2245,10 +2227,10 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
@@ -2260,7 +2242,7 @@
         <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2279,18 +2261,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2302,17 +2284,17 @@
       <c r="J22" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="10" t="n">
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M22" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M22" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2324,7 +2306,7 @@
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>19.5</v>
@@ -2345,10 +2327,10 @@
         <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>254.9</v>
+        <v>1.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2364,19 +2346,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E23" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>36.2</v>
+      <c r="F23" s="10" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
@@ -2387,14 +2369,14 @@
       <c r="J23" s="3" t="n">
         <v>52.9</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="10" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>92</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>82</v>
+        <v>93</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>92</v>
@@ -2418,13 +2400,13 @@
         <v>468</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>1123.5</v>
+        <v>123.5</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>935.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>26</v>
@@ -2433,7 +2415,7 @@
         <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>652.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2449,20 +2431,20 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="10" t="n">
         <v>29.1</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="10" t="n">
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2474,20 +2456,20 @@
       <c r="L24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="10" t="n">
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>5.4</v>
+        <v>25.4</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>84.09999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>20.7</v>
@@ -2496,25 +2478,25 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>13.6</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>11.1</v>
+        <v>24.7</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>10.1</v>
+        <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>118.9</v>
+        <v>18.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2530,22 +2512,22 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D25" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D25" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G25" s="11" t="n">
+      <c r="E25" s="10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1.2</v>
+        <v>19.6</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2557,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>11.8</v>
+        <v>17.6</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>16.3</v>
@@ -2571,10 +2553,10 @@
       <c r="P25" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q25" s="13" t="n">
+      <c r="Q25" s="8" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="10" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2584,7 +2566,7 @@
         <v>156.1</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="W25" s="3" t="n">
@@ -2594,7 +2576,7 @@
         <v>9.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2613,26 +2595,26 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="10" t="n">
         <v>11.6</v>
       </c>
-      <c r="H26" s="14" t="n">
-        <v>16.8</v>
+      <c r="H26" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>8</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2640,22 +2622,22 @@
       <c r="L26" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2667,7 +2649,7 @@
       <c r="U26" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2677,10 +2659,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>28.8</v>
+        <v>58.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2695,21 +2677,23 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="11" t="n">
+      <c r="C27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G27" s="3" t="n">
+      <c r="E27" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G27" s="10" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11</v>
+        <v>16.2</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
@@ -2718,40 +2702,40 @@
         <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>11.8</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R27" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="R27" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="V27" s="13" t="n">
-        <v>64.8</v>
+      <c r="V27" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>19.8</v>
@@ -2779,36 +2763,36 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G28" s="11" t="n">
+      <c r="E28" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G28" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="14" t="n">
-        <v>66</v>
+      <c r="H28" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>8.9</v>
+        <v>7.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="L28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2823,32 +2807,32 @@
       <c r="Q28" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.9</v>
+        <v>56.7</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>29.6</v>
+      <c r="V28" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2866,34 +2850,34 @@
       <c r="C29" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="E29" s="10" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G29" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="H29" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2908,26 +2892,26 @@
       <c r="Q29" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="14" t="n">
-        <v>19</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2949,26 +2933,26 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="10" t="n">
         <v>133.2</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="10" t="n">
         <v>85.8</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="10" t="n">
         <v>109.5</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="10" t="n">
         <v>47.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>280</v>
+        <v>22</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>39.8</v>
+        <v>33</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>308.4</v>
@@ -2976,7 +2960,7 @@
       <c r="L30" s="9" t="n">
         <v>9434.799999999999</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="10" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2991,7 +2975,7 @@
       <c r="Q30" s="9" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="11" t="n">
+      <c r="R30" s="10" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3001,19 +2985,19 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10.8</v>
+        <v>70.8</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>71.59999999999999</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>90.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>916.2</v>
+        <v>336.2</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>47.6</v>
@@ -3032,22 +3016,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D31" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D31" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" s="10" t="n">
         <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.6</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -3057,16 +3041,16 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M31" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M31" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>205.1</v>
+        <v>25.6</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -3074,19 +3058,19 @@
       <c r="Q31" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="9" t="n">
-        <v>10.4</v>
+      <c r="R31" s="10" t="n">
+        <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>59.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="V31" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="W31" s="9" t="n">
@@ -3096,10 +3080,10 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3115,16 +3099,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="E32" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="E32" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G32" s="10" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3134,46 +3118,46 @@
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L32" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="13" t="n">
+      <c r="Q32" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>96.8</v>
+        <v>56.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>198.1</v>
       </c>
-      <c r="V32" s="11" t="inlineStr"/>
-      <c r="W32" s="13" t="n">
+      <c r="V32" s="10" t="inlineStr"/>
+      <c r="W32" s="8" t="n">
         <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>4412.8</v>
+        <v>9119.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.8</v>
+        <v>26.2</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3192,16 +3176,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="10" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3211,16 +3195,16 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="14" t="n">
-        <v>19.6</v>
+      <c r="M33" s="10" t="n">
+        <v>15.6</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>16.7</v>
@@ -3238,15 +3222,15 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V33" s="11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="V33" s="10" t="n">
         <v>21.8</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3259,7 +3243,7 @@
         <v>75</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3275,16 +3259,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="13" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F34" s="3" t="n">
+      <c r="D34" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F34" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="10" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3296,13 +3280,13 @@
       <c r="J34" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L34" s="14" t="n">
+      <c r="K34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3327,9 +3311,9 @@
         <v>57.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="V34" s="11" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V34" s="10" t="n">
         <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3342,7 +3326,7 @@
         <v>67</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3357,42 +3341,44 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="n">
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D35" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="E35" s="13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G35" s="3" t="n">
+      <c r="E35" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G35" s="10" t="n">
         <v>6.6</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="14" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="M35" s="3" t="n">
+      <c r="L35" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.4</v>
@@ -3407,15 +3393,15 @@
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>82.2</v>
+        <v>62.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V35" s="11" t="n">
+      <c r="V35" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="14" t="n">
+      <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3425,7 +3411,7 @@
         <v>86.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3441,16 +3427,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3462,13 +3448,13 @@
       <c r="J36" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M36" s="3" t="n">
+      <c r="L36" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3483,7 +3469,7 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="14" t="n">
+      <c r="R36" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3493,9 +3479,9 @@
         <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="V36" s="10" t="n">
         <v>20.4</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3505,7 +3491,7 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3521,12 +3507,14 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="D37" s="9" t="n">
-        <v>120.8</v>
+        <v>132.8</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>8821.799999999999</v>
+        <v>882.1</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>11</v>
@@ -3543,10 +3531,10 @@
       <c r="J37" s="3" t="n">
         <v>31.5</v>
       </c>
-      <c r="K37" s="9" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="L37" s="9" t="n">
+      <c r="K37" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="M37" s="9" t="n">
@@ -3556,19 +3544,19 @@
         <v>0.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>20.8</v>
+        <v>30.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>149.4</v>
+        <v>14.4</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>131.8</v>
+        <v>133.8</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>1082.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1181.5</v>
+        <v>218.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3580,13 +3568,13 @@
         <v>109.8</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>998.1</v>
+        <v>95</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>101.4</v>
+        <v>1014.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3605,16 +3593,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3624,23 +3612,23 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>17.9</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.9</v>
+        <v>29.9</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>26.8</v>
@@ -3652,25 +3640,25 @@
         <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.4</v>
+        <v>0.1</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="10" t="n">
         <v>22</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>12790.1</v>
-      </c>
-      <c r="X38" s="14" t="n">
-        <v>111.9</v>
+        <v>11.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3686,15 +3674,15 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="E39" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3707,50 +3695,50 @@
       <c r="J39" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L39" s="3" t="n">
+      <c r="K39" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L39" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="10" t="n">
         <v>17.6</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q39" s="13" t="n">
+      <c r="Q39" s="8" t="n">
         <v>46.65</v>
       </c>
-      <c r="R39" s="13" t="n">
+      <c r="R39" s="10" t="n">
         <v>20.48</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="V39" s="13" t="n">
+      <c r="V39" s="8" t="n">
         <v>75.42999999999999</v>
       </c>
-      <c r="W39" s="11" t="n">
+      <c r="W39" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="X39" s="14" t="n">
+      <c r="X39" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.8</v>
+        <v>64.5</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>48.8</v>
@@ -3769,17 +3757,17 @@
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E40" s="11" t="n">
+      <c r="D40" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="E40" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>0.8</v>
+      <c r="F40" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>16.4</v>
@@ -3788,15 +3776,15 @@
         <v>2.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="L40" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3809,10 +3797,10 @@
         <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>20.8</v>
+        <v>26.2</v>
+      </c>
+      <c r="R40" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
@@ -3820,13 +3808,13 @@
       <c r="T40" s="3" t="n">
         <v>57.8</v>
       </c>
-      <c r="U40" s="14" t="n">
-        <v>94.40000000000001</v>
+      <c r="U40" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3850,16 +3838,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>21.9</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>20.1</v>
@@ -3868,55 +3856,55 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="10" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>15.2</v>
+      <c r="M41" s="10" t="n">
+        <v>17.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R41" s="3" t="n">
-        <v>17.8</v>
+      <c r="R41" s="10" t="n">
+        <v>17.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.9</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W41" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W41" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3933,34 +3921,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="13" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="E42" s="3" t="n">
+      <c r="D42" s="10" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E42" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="14" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>94</v>
+      <c r="F42" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M42" s="14" t="n">
+      <c r="L42" s="10" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M42" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -3975,7 +3963,7 @@
       <c r="Q42" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="10" t="n">
         <v>21</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -3990,17 +3978,17 @@
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="11" t="n">
+      <c r="W42" s="10" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1.4</v>
+        <v>14.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.4</v>
+        <v>57</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4016,20 +4004,20 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>174.4</v>
+      <c r="D43" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -4037,43 +4025,43 @@
       <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="14" t="n">
+      <c r="L43" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="14" t="n">
+      <c r="M43" s="10" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="R43" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="R43" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="S43" s="14" t="n">
-        <v>18</v>
+      <c r="S43" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="11" t="n">
+      <c r="W43" s="10" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4083,7 +4071,7 @@
         <v>14.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>21.9</v>
+        <v>57</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4099,51 +4087,51 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E44" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="F44" s="14" t="n">
-        <v>12</v>
+      <c r="F44" s="10" t="n">
+        <v>25</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>26.1</v>
+        <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K44" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K44" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
+      <c r="M44" s="10" t="n">
+        <v>15.6</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>154.8</v>
+        <v>298.6</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="R44" s="14" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R44" s="10" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4153,13 +4141,13 @@
         <v>47</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>2.3</v>
+        <v>23.2</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="11" t="n">
-        <v>20.6</v>
+      <c r="W44" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4168,7 +4156,7 @@
         <v>14.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>21</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4183,39 +4171,41 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="9" t="n">
-        <v>1165.8</v>
-      </c>
-      <c r="E45" s="9" t="n">
+      <c r="C45" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>102.8</v>
       </c>
-      <c r="F45" s="9" t="n">
-        <v>135.9</v>
-      </c>
-      <c r="G45" s="3" t="n">
+      <c r="F45" s="10" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="G45" s="10" t="n">
         <v>65</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>53.5</v>
+        <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>59.4</v>
+        <v>61.2</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>9.4</v>
       </c>
       <c r="L45" s="9" t="n">
         <v>109.6</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="10" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>499</v>
@@ -4227,31 +4217,31 @@
         <v>16.5</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>1191.1</v>
+        <v>121</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>115.2</v>
+        <v>116.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>517.9</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>187.1</v>
+        <v>107.1</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1543</v>
+        <v>143</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>111.5</v>
+        <v>115</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>392.9</v>
+        <v>393.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>11141.1</v>
+        <v>114</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4267,17 +4257,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="10" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="10" t="n">
         <v>22.5</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>19.8</v>
+      <c r="G46" s="10" t="n">
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4289,31 +4279,31 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>72162.8</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="14" t="n">
-        <v>54.9</v>
+      <c r="N46" s="3" t="n">
+        <v>2011</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>17.8</v>
+        <v>26.2</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="14" t="n">
-        <v>19.8</v>
+      <c r="S46" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>53</v>
@@ -4324,7 +4314,7 @@
       <c r="V46" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="10" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
@@ -4334,7 +4324,7 @@
         <v>3.6</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
